--- a/artfynd/A 32105-2026 artfynd.xlsx
+++ b/artfynd/A 32105-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,53 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63028160</v>
+        <v>135754442</v>
       </c>
       <c r="B2" t="n">
-        <v>4775</v>
+        <v>92048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lumpen, 400m NV, Upl</t>
+          <t>Lumpen NV, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626742</v>
+        <v>626728</v>
       </c>
       <c r="R2" t="n">
-        <v>6649580</v>
+        <v>6649502</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,79 +771,69 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>torrgran i äldre blandskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63028160</t>
+          <t>https://artportalen.se/Sighting/135754442</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63028164</v>
+        <v>135754443</v>
       </c>
       <c r="B3" t="n">
-        <v>4775</v>
+        <v>92048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lumpen, 400m NV, Upl</t>
+          <t>Lumpen NV, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626738</v>
+        <v>626727</v>
       </c>
       <c r="R3" t="n">
-        <v>6649412</v>
+        <v>6649500</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,79 +883,69 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>torrgran i äldre blandskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63028164</t>
+          <t>https://artportalen.se/Sighting/135754443</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63028168</v>
+        <v>135754444</v>
       </c>
       <c r="B4" t="n">
-        <v>4775</v>
+        <v>92048</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lumpen, 400m NV, Upl</t>
+          <t>Lumpen NV, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626729</v>
+        <v>626732</v>
       </c>
       <c r="R4" t="n">
-        <v>6649438</v>
+        <v>6649490</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,12 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,79 +995,69 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>torrgran i äldre blandskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63028168</t>
+          <t>https://artportalen.se/Sighting/135754444</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>63028159</v>
+        <v>135754446</v>
       </c>
       <c r="B5" t="n">
-        <v>5179</v>
+        <v>92048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lumpen, 400m NV, Upl</t>
+          <t>Lumpen NV, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626742</v>
+        <v>626713</v>
       </c>
       <c r="R5" t="n">
-        <v>6649580</v>
+        <v>6649507</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,12 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,79 +1107,69 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>torrgran i äldre blandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63028159</t>
+          <t>https://artportalen.se/Sighting/135754446</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>63028163</v>
+        <v>135754450</v>
       </c>
       <c r="B6" t="n">
-        <v>5179</v>
+        <v>92048</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lumpen, 400m NV, Upl</t>
+          <t>Lumpen NV, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626738</v>
+        <v>626714</v>
       </c>
       <c r="R6" t="n">
-        <v>6649412</v>
+        <v>6649484</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,12 +1193,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,79 +1219,69 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>torrgran i äldre blandskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63028163</t>
+          <t>https://artportalen.se/Sighting/135754450</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>63028167</v>
+        <v>135754452</v>
       </c>
       <c r="B7" t="n">
-        <v>5179</v>
+        <v>92048</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lumpen, 400m NV, Upl</t>
+          <t>Lumpen NV, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626729</v>
+        <v>626724</v>
       </c>
       <c r="R7" t="n">
-        <v>6649438</v>
+        <v>6649485</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,12 +1305,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,79 +1331,69 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>torrgran i äldre blandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63028167</t>
+          <t>https://artportalen.se/Sighting/135754452</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>63028170</v>
+        <v>135754453</v>
       </c>
       <c r="B8" t="n">
-        <v>5179</v>
+        <v>92048</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lumpen, 400m NV, Upl</t>
+          <t>Lumpen NV, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626655</v>
+        <v>626744</v>
       </c>
       <c r="R8" t="n">
-        <v>6649355</v>
+        <v>6649490</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,12 +1417,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,36 +1443,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>torrgran i äldre blandskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63028170</t>
+          <t>https://artportalen.se/Sighting/135754453</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>79085712</v>
+        <v>135754455</v>
       </c>
       <c r="B9" t="n">
-        <v>5435</v>
+        <v>92048</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,54 +1475,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101859</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalvingad blombock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Strangalia attenuata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gubbslåtter, Upl</t>
+          <t>Lumpen NV, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626861</v>
+        <v>626728</v>
       </c>
       <c r="R9" t="n">
-        <v>6649699</v>
+        <v>6649438</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1546,27 +1529,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På blommande strätta</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,34 +1553,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Thomas Persson Vinnersten</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thomas Persson Vinnersten</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79085712</t>
+          <t>https://artportalen.se/Sighting/135754455</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>86969721</v>
+        <v>135754467</v>
       </c>
       <c r="B10" t="n">
-        <v>5435</v>
+        <v>92048</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,54 +1587,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101859</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalvingad blombock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Strangalia attenuata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Möjsjön, Upl</t>
+          <t>Lumpen NV, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626778</v>
+        <v>626734</v>
       </c>
       <c r="R10" t="n">
-        <v>6649715</v>
+        <v>6649468</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1681,17 +1641,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-07-19</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-07-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gebomsök längs vägkanten av blommande älggräs och strätta. Ca 25 grader, kl 12:15. En individ på blommande strätta.</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,38 +1665,33 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Thomas Persson Vinnersten</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Thomas Persson Vinnersten</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Faunaväkteri småkryp</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86969721</t>
+          <t>https://artportalen.se/Sighting/135754467</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>87440839</v>
+        <v>135764428</v>
       </c>
       <c r="B11" t="n">
-        <v>5435</v>
+        <v>92048</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,58 +1699,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101859</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalvingad blombock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Strangalia attenuata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>S Mörtsjön, Upl</t>
+          <t>NV Lumpen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626789</v>
+        <v>626720</v>
       </c>
       <c r="R11" t="n">
-        <v>6649726</v>
+        <v>6649444</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1814,12 +1753,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-08-13</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-08-13</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre fruktkrp på snart barklös granlåga.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,39 +1782,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>Petter Andersson</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87440839</t>
+          <t>https://artportalen.se/Sighting/135764428</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111016024</v>
+        <v>135764429</v>
       </c>
       <c r="B12" t="n">
-        <v>5435</v>
+        <v>92048</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,62 +1816,48 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101859</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalvingad blombock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Strangalia attenuata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Styggkärrets naturreservat, Styggkärret (Styggkärrets NR), Upl</t>
+          <t>NV Lumpen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626801</v>
+        <v>626749</v>
       </c>
       <c r="R12" t="n">
-        <v>6649721</v>
+        <v>6649499</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1947,22 +1881,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,86 +1912,76 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marianne Lindgren</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marianne Lindgren</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111016024</t>
+          <t>https://artportalen.se/Sighting/135764429</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>79085721</v>
+        <v>135764430</v>
       </c>
       <c r="B13" t="n">
-        <v>5173</v>
+        <v>92480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102185</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gubbslåtter, Upl</t>
+          <t>NV Lumpen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626861</v>
+        <v>626744</v>
       </c>
       <c r="R13" t="n">
-        <v>6649699</v>
+        <v>6649494</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2081,27 +2005,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På blommande strätta</t>
+          <t>Gammalt och torrt.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2117,27 +2041,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Thomas Persson Vinnersten</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Thomas Persson Vinnersten</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79085721</t>
+          <t>https://artportalen.se/Sighting/135764430</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>63028161</v>
+        <v>135764431</v>
       </c>
       <c r="B14" t="n">
-        <v>5178</v>
+        <v>92480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,42 +2069,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102204</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lumpen, 400m NV, Upl</t>
+          <t>NV Lumpen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626735</v>
+        <v>626751</v>
       </c>
       <c r="R14" t="n">
-        <v>6649592</v>
+        <v>6649510</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2204,12 +2123,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2220,79 +2149,69 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>grovgrenig gran i äldre blandskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63028161</t>
+          <t>https://artportalen.se/Sighting/135764431</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>63028162</v>
+        <v>135754454</v>
       </c>
       <c r="B15" t="n">
-        <v>5178</v>
+        <v>92392</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102204</v>
+        <v>2062</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lumpen, 400m NV, Upl</t>
+          <t>Lumpen NV, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626761</v>
+        <v>626731</v>
       </c>
       <c r="R15" t="n">
-        <v>6649419</v>
+        <v>6649439</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2316,12 +2235,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2332,79 +2261,69 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>grovgrenig gran i äldre blandskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63028162</t>
+          <t>https://artportalen.se/Sighting/135754454</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>63028166</v>
+        <v>135754462</v>
       </c>
       <c r="B16" t="n">
-        <v>5178</v>
+        <v>92392</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102204</v>
+        <v>2062</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lumpen, 400m NV, Upl</t>
+          <t>Lumpen NV, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626728</v>
+        <v>626735</v>
       </c>
       <c r="R16" t="n">
-        <v>6649420</v>
+        <v>6649434</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2428,12 +2347,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2444,36 +2373,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>grovgrenig gran i äldre blandskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63028166</t>
+          <t>https://artportalen.se/Sighting/135754462</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>63028165</v>
+        <v>135754460</v>
       </c>
       <c r="B17" t="n">
-        <v>5199</v>
+        <v>92011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,42 +2405,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lumpen, 400m NV, Upl</t>
+          <t>Lumpen NV, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626738</v>
+        <v>626743</v>
       </c>
       <c r="R17" t="n">
-        <v>6649412</v>
+        <v>6649409</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2540,12 +2459,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2556,36 +2485,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>torrgran i äldre blandskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63028165</t>
+          <t>https://artportalen.se/Sighting/135754460</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>63028169</v>
+        <v>135754465</v>
       </c>
       <c r="B18" t="n">
-        <v>5199</v>
+        <v>92011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,42 +2517,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lumpen, 400m NV, Upl</t>
+          <t>Lumpen NV, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626729</v>
+        <v>626659</v>
       </c>
       <c r="R18" t="n">
-        <v>6649438</v>
+        <v>6649359</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2652,12 +2571,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2668,27 +2597,4512 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>torrgran i äldre blandskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135754465</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135754466</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>626673</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6649392</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754466</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>63028160</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lumpen, 400m NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>626742</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6649580</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>torrgran i äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63028160</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>63028164</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lumpen, 400m NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>626738</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6649412</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>torrgran i äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63028164</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>63028168</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lumpen, 400m NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>626729</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6649438</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>torrgran i äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63028168</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>63028159</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lumpen, 400m NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>626742</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6649580</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>torrgran i äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63028159</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>63028163</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lumpen, 400m NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>626738</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6649412</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>torrgran i äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63028163</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>63028167</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lumpen, 400m NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>626729</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6649438</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>torrgran i äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63028167</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>63028170</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lumpen, 400m NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>626655</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6649355</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>torrgran i äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63028170</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135754441</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>626730</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6649518</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754441</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135754457</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>626740</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6649413</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754457</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135754464</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>626699</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6649378</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754464</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>79085712</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5435</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>101859</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Smalvingad blombock</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Strangalia attenuata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gubbslåtter, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>626861</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6649699</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På blommande strätta</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Thomas Persson Vinnersten</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Thomas Persson Vinnersten</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79085712</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>86969721</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5435</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>101859</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Smalvingad blombock</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Strangalia attenuata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Möjsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>626778</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6649715</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2020-07-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2020-07-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Gebomsök längs vägkanten av blommande älggräs och strätta. Ca 25 grader, kl 12:15. En individ på blommande strätta.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Thomas Persson Vinnersten</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Thomas Persson Vinnersten</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Faunaväkteri småkryp</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86969721</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>87440839</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5435</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>101859</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Smalvingad blombock</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Strangalia attenuata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>S Mörtsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>626789</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6649726</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2020-08-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2020-08-13</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87440839</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>111016024</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5435</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>101859</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Smalvingad blombock</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Strangalia attenuata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Styggkärrets naturreservat, Styggkärret (Styggkärrets NR), Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>626801</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6649721</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-07-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-07-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Marianne Lindgren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Marianne Lindgren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111016024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135400278</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5437</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>101859</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Smalvingad blombock</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Strangalia attenuata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>S om Mörtsjön, vägkorsning, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>626779</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6649713</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135400278</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>79085721</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5173</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>102185</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Myskbock</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Aromia moschata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gubbslåtter, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>626861</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6649699</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På blommande strätta</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Thomas Persson Vinnersten</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Thomas Persson Vinnersten</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79085721</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135400281</v>
+      </c>
+      <c r="B36" t="n">
+        <v>5175</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>102185</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Myskbock</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Aromia moschata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>S om Mörtsjön, vägkorsning, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>626779</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6649713</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135400281</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>63028161</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lumpen, 400m NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>626735</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6649592</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>grovgrenig gran i äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63028161</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>63028162</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lumpen, 400m NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>626761</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6649419</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>grovgrenig gran i äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63028162</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>63028166</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lumpen, 400m NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>626728</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6649420</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>grovgrenig gran i äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63028166</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135754456</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4782</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>626732</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6649422</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754456</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135754461</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4782</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>626742</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6649411</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754461</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135764426</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>NV Lumpen, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>626675</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6649379</v>
+      </c>
+      <c r="S42" t="n">
+        <v>8</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst två individer, täh täh lätet. Två individer hördes strax efteråt både från "sankmarken" åt SV och SO om moränhöjningen.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135764426</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>63028165</v>
+      </c>
+      <c r="B43" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lumpen, 400m NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>626738</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6649412</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>torrgran i äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63028165</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>63028169</v>
+      </c>
+      <c r="B44" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lumpen, 400m NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>626729</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6649438</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2017-01-26</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>torrgran i äldre blandskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/63028169</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135754445</v>
+      </c>
+      <c r="B45" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>626723</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6649493</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754445</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135754458</v>
+      </c>
+      <c r="B46" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>626740</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6649413</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754458</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135754440</v>
+      </c>
+      <c r="B47" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>626763</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6649672</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754440</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135754469</v>
+      </c>
+      <c r="B48" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>626774</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6649491</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754469</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135751224</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gubbslåtter, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>626766</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6649484</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 25 bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135751224</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135754448</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>626708</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6649497</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754448</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135754449</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>626709</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6649491</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754449</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135754451</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>626714</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6649484</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754451</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135754468</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>626761</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6649465</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754468</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135754470</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>626777</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6649524</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754470</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135754471</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>626780</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6649548</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754471</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135754459</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92067</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6332881</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lumpen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>626739</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6649411</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135754459</t>
         </is>
       </c>
     </row>
@@ -2711,6 +7125,44 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32105-2026 artfynd.xlsx
+++ b/artfynd/A 32105-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754442</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754443</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754444</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754446</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754450</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135754452</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135754453</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135754455</v>
       </c>
       <c r="B9" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135754467</v>
       </c>
       <c r="B10" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135764428</v>
       </c>
       <c r="B11" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135764429</v>
       </c>
       <c r="B12" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135764430</v>
       </c>
       <c r="B13" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>135764431</v>
       </c>
       <c r="B14" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135754454</v>
       </c>
       <c r="B15" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>135754462</v>
       </c>
       <c r="B16" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>135754460</v>
       </c>
       <c r="B17" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>135754465</v>
       </c>
       <c r="B18" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135754466</v>
       </c>
       <c r="B19" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135751224</v>
       </c>
       <c r="B49" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>135754448</v>
       </c>
       <c r="B50" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>135754449</v>
       </c>
       <c r="B51" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>135754451</v>
       </c>
       <c r="B52" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>135754468</v>
       </c>
       <c r="B53" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>135754470</v>
       </c>
       <c r="B54" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135754471</v>
       </c>
       <c r="B55" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>135754459</v>
       </c>
       <c r="B56" t="n">
-        <v>92067</v>
+        <v>92069</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 32105-2026 artfynd.xlsx
+++ b/artfynd/A 32105-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754442</v>
       </c>
       <c r="B2" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754443</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754444</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754446</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754450</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135754452</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135754453</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135754455</v>
       </c>
       <c r="B9" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135754467</v>
       </c>
       <c r="B10" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135764428</v>
       </c>
       <c r="B11" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135764429</v>
       </c>
       <c r="B12" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135764430</v>
       </c>
       <c r="B13" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>135764431</v>
       </c>
       <c r="B14" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135754454</v>
       </c>
       <c r="B15" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>135754462</v>
       </c>
       <c r="B16" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>135754460</v>
       </c>
       <c r="B17" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>135754465</v>
       </c>
       <c r="B18" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135754466</v>
       </c>
       <c r="B19" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>135754441</v>
       </c>
       <c r="B27" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>135754457</v>
       </c>
       <c r="B28" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>135754464</v>
       </c>
       <c r="B29" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>135400278</v>
       </c>
       <c r="B34" t="n">
-        <v>5437</v>
+        <v>5438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>135400281</v>
       </c>
       <c r="B36" t="n">
-        <v>5175</v>
+        <v>5176</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>135754456</v>
       </c>
       <c r="B40" t="n">
-        <v>4782</v>
+        <v>4783</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>135754461</v>
       </c>
       <c r="B41" t="n">
-        <v>4782</v>
+        <v>4783</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>135764426</v>
       </c>
       <c r="B42" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>135754445</v>
       </c>
       <c r="B45" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>135754458</v>
       </c>
       <c r="B46" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>135754440</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>8452</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135754469</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>8452</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135751224</v>
       </c>
       <c r="B49" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>135754448</v>
       </c>
       <c r="B50" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>135754449</v>
       </c>
       <c r="B51" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>135754451</v>
       </c>
       <c r="B52" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>135754468</v>
       </c>
       <c r="B53" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>135754470</v>
       </c>
       <c r="B54" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135754471</v>
       </c>
       <c r="B55" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>135754459</v>
       </c>
       <c r="B56" t="n">
-        <v>92069</v>
+        <v>92083</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 32105-2026 artfynd.xlsx
+++ b/artfynd/A 32105-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754442</v>
       </c>
       <c r="B2" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754443</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754444</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754446</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754450</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135754452</v>
       </c>
       <c r="B7" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135754453</v>
       </c>
       <c r="B8" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135754455</v>
       </c>
       <c r="B9" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135754467</v>
       </c>
       <c r="B10" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135764428</v>
       </c>
       <c r="B11" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135764429</v>
       </c>
       <c r="B12" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135764430</v>
       </c>
       <c r="B13" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>135764431</v>
       </c>
       <c r="B14" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135754454</v>
       </c>
       <c r="B15" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>135754462</v>
       </c>
       <c r="B16" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>135754460</v>
       </c>
       <c r="B17" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>135754465</v>
       </c>
       <c r="B18" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135754466</v>
       </c>
       <c r="B19" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135751224</v>
       </c>
       <c r="B49" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>135754448</v>
       </c>
       <c r="B50" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>135754449</v>
       </c>
       <c r="B51" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>135754451</v>
       </c>
       <c r="B52" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>135754468</v>
       </c>
       <c r="B53" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>135754470</v>
       </c>
       <c r="B54" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135754471</v>
       </c>
       <c r="B55" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>135754459</v>
       </c>
       <c r="B56" t="n">
-        <v>92083</v>
+        <v>92084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 32105-2026 artfynd.xlsx
+++ b/artfynd/A 32105-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754442</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754443</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754444</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754446</v>
       </c>
       <c r="B5" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754450</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135754452</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135754453</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135754455</v>
       </c>
       <c r="B9" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135754467</v>
       </c>
       <c r="B10" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135764428</v>
       </c>
       <c r="B11" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135764429</v>
       </c>
       <c r="B12" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135764430</v>
       </c>
       <c r="B13" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>135764431</v>
       </c>
       <c r="B14" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135754454</v>
       </c>
       <c r="B15" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>135754462</v>
       </c>
       <c r="B16" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>135754460</v>
       </c>
       <c r="B17" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>135754465</v>
       </c>
       <c r="B18" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135754466</v>
       </c>
       <c r="B19" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135751224</v>
       </c>
       <c r="B49" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>135754448</v>
       </c>
       <c r="B50" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>135754449</v>
       </c>
       <c r="B51" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>135754451</v>
       </c>
       <c r="B52" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>135754468</v>
       </c>
       <c r="B53" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>135754470</v>
       </c>
       <c r="B54" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135754471</v>
       </c>
       <c r="B55" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>135754459</v>
       </c>
       <c r="B56" t="n">
-        <v>92084</v>
+        <v>92085</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 32105-2026 artfynd.xlsx
+++ b/artfynd/A 32105-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754442</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754443</v>
       </c>
       <c r="B3" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754444</v>
       </c>
       <c r="B4" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754446</v>
       </c>
       <c r="B5" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754450</v>
       </c>
       <c r="B6" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135754452</v>
       </c>
       <c r="B7" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135754453</v>
       </c>
       <c r="B8" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135754455</v>
       </c>
       <c r="B9" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135754467</v>
       </c>
       <c r="B10" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135764428</v>
       </c>
       <c r="B11" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135764429</v>
       </c>
       <c r="B12" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135764430</v>
       </c>
       <c r="B13" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>135764431</v>
       </c>
       <c r="B14" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135754454</v>
       </c>
       <c r="B15" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>135754462</v>
       </c>
       <c r="B16" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>135754460</v>
       </c>
       <c r="B17" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>135754465</v>
       </c>
       <c r="B18" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135754466</v>
       </c>
       <c r="B19" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>135764426</v>
       </c>
       <c r="B42" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135751224</v>
       </c>
       <c r="B49" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>135754448</v>
       </c>
       <c r="B50" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>135754449</v>
       </c>
       <c r="B51" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>135754451</v>
       </c>
       <c r="B52" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>135754468</v>
       </c>
       <c r="B53" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>135754470</v>
       </c>
       <c r="B54" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135754471</v>
       </c>
       <c r="B55" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>135754459</v>
       </c>
       <c r="B56" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 32105-2026 artfynd.xlsx
+++ b/artfynd/A 32105-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754442</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754443</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754444</v>
       </c>
       <c r="B4" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754446</v>
       </c>
       <c r="B5" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754450</v>
       </c>
       <c r="B6" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135754452</v>
       </c>
       <c r="B7" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135754453</v>
       </c>
       <c r="B8" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135754455</v>
       </c>
       <c r="B9" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135754467</v>
       </c>
       <c r="B10" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135764428</v>
       </c>
       <c r="B11" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135764429</v>
       </c>
       <c r="B12" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135764430</v>
       </c>
       <c r="B13" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>135764431</v>
       </c>
       <c r="B14" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135754454</v>
       </c>
       <c r="B15" t="n">
-        <v>92409</v>
+        <v>92415</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>135754462</v>
       </c>
       <c r="B16" t="n">
-        <v>92409</v>
+        <v>92415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>135754460</v>
       </c>
       <c r="B17" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>135754465</v>
       </c>
       <c r="B18" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135754466</v>
       </c>
       <c r="B19" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>135764426</v>
       </c>
       <c r="B42" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135751224</v>
       </c>
       <c r="B49" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>135754448</v>
       </c>
       <c r="B50" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>135754449</v>
       </c>
       <c r="B51" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>135754451</v>
       </c>
       <c r="B52" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>135754468</v>
       </c>
       <c r="B53" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>135754470</v>
       </c>
       <c r="B54" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135754471</v>
       </c>
       <c r="B55" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>135754459</v>
       </c>
       <c r="B56" t="n">
-        <v>92086</v>
+        <v>92092</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 32105-2026 artfynd.xlsx
+++ b/artfynd/A 32105-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754442</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754443</v>
       </c>
       <c r="B3" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754444</v>
       </c>
       <c r="B4" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754446</v>
       </c>
       <c r="B5" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754450</v>
       </c>
       <c r="B6" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135754452</v>
       </c>
       <c r="B7" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135754453</v>
       </c>
       <c r="B8" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135754455</v>
       </c>
       <c r="B9" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135754467</v>
       </c>
       <c r="B10" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135764428</v>
       </c>
       <c r="B11" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135764429</v>
       </c>
       <c r="B12" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135764430</v>
       </c>
       <c r="B13" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>135764431</v>
       </c>
       <c r="B14" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135754454</v>
       </c>
       <c r="B15" t="n">
-        <v>92415</v>
+        <v>92416</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>135754462</v>
       </c>
       <c r="B16" t="n">
-        <v>92415</v>
+        <v>92416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>135754460</v>
       </c>
       <c r="B17" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>135754465</v>
       </c>
       <c r="B18" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135754466</v>
       </c>
       <c r="B19" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>135764426</v>
       </c>
       <c r="B42" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135751224</v>
       </c>
       <c r="B49" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>135754448</v>
       </c>
       <c r="B50" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>135754449</v>
       </c>
       <c r="B51" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>135754451</v>
       </c>
       <c r="B52" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>135754468</v>
       </c>
       <c r="B53" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>135754470</v>
       </c>
       <c r="B54" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135754471</v>
       </c>
       <c r="B55" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>135754459</v>
       </c>
       <c r="B56" t="n">
-        <v>92092</v>
+        <v>92093</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 32105-2026 artfynd.xlsx
+++ b/artfynd/A 32105-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754442</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754443</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754444</v>
       </c>
       <c r="B4" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754446</v>
       </c>
       <c r="B5" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754450</v>
       </c>
       <c r="B6" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135754452</v>
       </c>
       <c r="B7" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135754453</v>
       </c>
       <c r="B8" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135754455</v>
       </c>
       <c r="B9" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135754467</v>
       </c>
       <c r="B10" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135764428</v>
       </c>
       <c r="B11" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135764429</v>
       </c>
       <c r="B12" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135764430</v>
       </c>
       <c r="B13" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>135764431</v>
       </c>
       <c r="B14" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135754454</v>
       </c>
       <c r="B15" t="n">
-        <v>92416</v>
+        <v>92422</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>135754462</v>
       </c>
       <c r="B16" t="n">
-        <v>92416</v>
+        <v>92422</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>135754460</v>
       </c>
       <c r="B17" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>135754465</v>
       </c>
       <c r="B18" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135754466</v>
       </c>
       <c r="B19" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135751224</v>
       </c>
       <c r="B49" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>135754448</v>
       </c>
       <c r="B50" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>135754449</v>
       </c>
       <c r="B51" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>135754451</v>
       </c>
       <c r="B52" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>135754468</v>
       </c>
       <c r="B53" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>135754470</v>
       </c>
       <c r="B54" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135754471</v>
       </c>
       <c r="B55" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>135754459</v>
       </c>
       <c r="B56" t="n">
-        <v>92093</v>
+        <v>92099</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 32105-2026 artfynd.xlsx
+++ b/artfynd/A 32105-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135754442</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135754443</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135754444</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135754446</v>
       </c>
       <c r="B5" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135754450</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135754452</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135754453</v>
       </c>
       <c r="B8" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135754455</v>
       </c>
       <c r="B9" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135754467</v>
       </c>
       <c r="B10" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135764428</v>
       </c>
       <c r="B11" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135764429</v>
       </c>
       <c r="B12" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135764430</v>
       </c>
       <c r="B13" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>135764431</v>
       </c>
       <c r="B14" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>135754454</v>
       </c>
       <c r="B15" t="n">
-        <v>92422</v>
+        <v>92429</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>135754462</v>
       </c>
       <c r="B16" t="n">
-        <v>92422</v>
+        <v>92429</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>135754460</v>
       </c>
       <c r="B17" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>135754465</v>
       </c>
       <c r="B18" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135754466</v>
       </c>
       <c r="B19" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>135764426</v>
       </c>
       <c r="B42" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135751224</v>
       </c>
       <c r="B49" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>135754448</v>
       </c>
       <c r="B50" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>135754449</v>
       </c>
       <c r="B51" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>135754451</v>
       </c>
       <c r="B52" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>135754468</v>
       </c>
       <c r="B53" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>135754470</v>
       </c>
       <c r="B54" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135754471</v>
       </c>
       <c r="B55" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>135754459</v>
       </c>
       <c r="B56" t="n">
-        <v>92099</v>
+        <v>92106</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
